--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104672_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104672_W24.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5815</v>
+        <v>5.3988</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8181</v>
+        <v>3.7252</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7634</v>
+        <v>1.6736</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5475</v>
+        <v>1.5437</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0593</v>
+        <v>2.0484</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5117</v>
+        <v>-0.5047</v>
       </c>
       <c r="J2" t="n">
-        <v>3.625</v>
+        <v>3.5945</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5877</v>
+        <v>3.5573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0774</v>
+        <v>-2.0508</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5284</v>
+        <v>-1.5089</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7975</v>
+        <v>1.6353</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5425</v>
+        <v>0.506</v>
       </c>
       <c r="U2" t="n">
-        <v>2.255</v>
+        <v>1.1294</v>
       </c>
       <c r="V2" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1829</v>
+        <v>1.7273</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7433</v>
+        <v>-0.0424</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5605</v>
+        <v>1.7697</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6037</v>
+        <v>0.7786</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9768</v>
+        <v>1.9715</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3732</v>
+        <v>-1.1929</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4027</v>
+        <v>2.6423</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4027</v>
+        <v>3.3947</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.7524</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.799</v>
+        <v>-1.8637</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4258</v>
+        <v>-1.4232</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3732</v>
+        <v>-0.4405</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2268</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4865</v>
+        <v>1.1567</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3822</v>
+        <v>0.0273</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1043</v>
+        <v>1.1294</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5392</v>
+        <v>0.3989</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0579</v>
+        <v>1.7886</v>
       </c>
       <c r="F4" t="n">
-        <v>1.597</v>
+        <v>-1.3898</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7951</v>
+        <v>0.6069</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9945</v>
+        <v>0.9792</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1994</v>
+        <v>-0.3724</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6961</v>
+        <v>1.3962</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4451</v>
+        <v>1.3962</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.749</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.901</v>
+        <v>-0.7893</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4506</v>
+        <v>-0.4169</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4504</v>
+        <v>-0.3724</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0556</v>
+        <v>0.7025</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0585</v>
+        <v>0.4411</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0029</v>
+        <v>0.2614</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1172</v>
+        <v>-0.0418</v>
       </c>
       <c r="E5" t="n">
-        <v>0.727</v>
+        <v>-1.0486</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8442</v>
+        <v>1.0068</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7806999999999999</v>
+        <v>-2.7212</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7806999999999999</v>
+        <v>-0.3419</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-2.3792</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7966</v>
+        <v>-1.2295</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7966</v>
+        <v>0.5064</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.7359</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0159</v>
+        <v>-1.4916</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0159</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.6433</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1948</v>
+        <v>0.907</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0696</v>
+        <v>0.2296</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2643</v>
+        <v>0.6774</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.2413</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6482</v>
+        <v>0.7232</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2425</v>
+        <v>-0.9645</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0574</v>
+        <v>0.7785</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1933</v>
+        <v>0.7785</v>
       </c>
       <c r="I6" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1083</v>
+        <v>0.7929</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1456</v>
+        <v>0.7929</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.051</v>
+        <v>-0.0144</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0477</v>
+        <v>-0.0144</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09859999999999999</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8072</v>
+        <v>0.0697</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5958</v>
+        <v>-0.0697</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2114</v>
+        <v>0.1394</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0246</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.599</v>
+        <v>-0.9083</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6065</v>
+        <v>0.2868</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0075</v>
+        <v>-1.1951</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7173</v>
+        <v>-0.0565</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3449</v>
+        <v>-0.1952</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3724</v>
+        <v>0.1387</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2021</v>
+        <v>-0.1146</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5226</v>
+        <v>-0.1519</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.7247</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5152</v>
+        <v>0.0581</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8675</v>
+        <v>-0.0433</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3451</v>
+        <v>0.4866</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3629</v>
+        <v>0.2437</v>
       </c>
       <c r="U7" t="n">
-        <v>0.708</v>
+        <v>0.2429</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>-2.0212</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4832</v>
+        <v>-1.1101</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8013</v>
+        <v>-2.0256</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6819</v>
+        <v>0.9155</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1074</v>
+        <v>-4.5745</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7693</v>
+        <v>-1.5546</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3381</v>
+        <v>-3.0199</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5412</v>
+        <v>-3.3422</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2078</v>
+        <v>-0.5483</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.749</v>
+        <v>-2.7939</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5662</v>
+        <v>-1.2323</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9771</v>
+        <v>-1.0062</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5891</v>
+        <v>-0.226</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0278</v>
+        <v>0.7815</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2601</v>
+        <v>0.2271</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2323</v>
+        <v>0.5543</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4822</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9016</v>
+        <v>-1.1587</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3774</v>
+        <v>-0.569</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4758</v>
+        <v>-0.5897</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.5782</v>
+        <v>-2.0953</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5687</v>
+        <v>-0.7561</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0095</v>
+        <v>-1.3392</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.3189</v>
+        <v>-0.5456</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5439000000000001</v>
+        <v>0.2068</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.775</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2593</v>
+        <v>-1.5497</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0248</v>
+        <v>-0.9629</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2345</v>
+        <v>-0.5868</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0039</v>
+        <v>0.2717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1512</v>
+        <v>-0.0234</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1473</v>
+        <v>0.2951</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0927</v>
+        <v>-0.4733</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.554</v>
+        <v>-2.8301</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.396</v>
+        <v>-1.8548</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.158</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3369</v>
+        <v>-4.3247</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7878</v>
+        <v>-3.7828</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.134</v>
+        <v>-2.1448</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.134</v>
+        <v>-2.1448</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2029</v>
+        <v>-2.1799</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8756</v>
+        <v>0.5841</v>
       </c>
       <c r="T10" t="n">
-        <v>0.738</v>
+        <v>0.29</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1376</v>
+        <v>0.294</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7484</v>
+        <v>-2.8513</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1664</v>
+        <v>-3.6222</v>
       </c>
       <c r="F11" t="n">
-        <v>0.418</v>
+        <v>0.7709</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7957</v>
+        <v>-3.8011</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8685</v>
+        <v>-1.8751</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9272</v>
+        <v>-1.926</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5682</v>
+        <v>-2.5977</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0328</v>
+        <v>-1.0557</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2275</v>
+        <v>-1.2034</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4537</v>
+        <v>0.4506</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3811</v>
+        <v>0.2111</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0726</v>
+        <v>0.2396</v>
       </c>
       <c r="V11" t="n">
-        <v>2.0888</v>
+        <v>2.0926</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0965</v>
+        <v>-0.0863</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.4042</v>
+        <v>-6.7876</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5479</v>
+        <v>-6.9955</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1437</v>
+        <v>0.2079</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8997</v>
+        <v>-3.9193</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0763</v>
+        <v>-2.0819</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8233</v>
+        <v>-1.8373</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2858</v>
+        <v>-2.3262</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8943</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3915</v>
+        <v>-1.4084</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6139</v>
+        <v>-1.5931</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3269</v>
+        <v>0.317</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8861</v>
+        <v>-0.2744</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5592</v>
+        <v>0.5914</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.0983</v>
+        <v>-8.404200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.0168</v>
+        <v>-9.6343</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9182999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.7656</v>
+        <v>-17.7849</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7975</v>
+        <v>-4.81</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.9678</v>
+        <v>-12.9748</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.6381</v>
+        <v>-3.874699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>5.211899999999999</v>
+        <v>5.0358</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.85</v>
+        <v>-8.910599999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.1273</v>
+        <v>-13.9101</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.0095</v>
+        <v>-9.845699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.117900000000001</v>
+        <v>-4.064299999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4024</v>
+        <v>-3.414399999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0126</v>
+        <v>-17.0725</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6101</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6388</v>
+        <v>7.3627</v>
       </c>
       <c r="T13" t="n">
-        <v>1.089</v>
+        <v>1.8084</v>
       </c>
       <c r="U13" t="n">
-        <v>5.549699999999999</v>
+        <v>5.5543</v>
       </c>
       <c r="V13" t="n">
-        <v>5.431</v>
+        <v>5.4325</v>
       </c>
       <c r="W13" t="n">
-        <v>9.545</v>
+        <v>9.5047</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.114</v>
+        <v>-4.0722</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6443</v>
+        <v>6.1082</v>
       </c>
       <c r="E14" t="n">
-        <v>4.561</v>
+        <v>4.7328</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0833</v>
+        <v>1.3754</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2371</v>
+        <v>4.2213</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7822</v>
+        <v>1.7726</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4549</v>
+        <v>2.4487</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2832</v>
+        <v>4.2363</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8706</v>
+        <v>2.8366</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0461</v>
+        <v>-0.015</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0884</v>
+        <v>-1.064</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1411</v>
+        <v>-0.6562</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0948</v>
+        <v>-0.8598</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0463</v>
+        <v>0.2036</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7414</v>
+        <v>4.9132</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3138</v>
+        <v>-0.2126</v>
       </c>
       <c r="F15" t="n">
-        <v>5.0552</v>
+        <v>5.1258</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8908</v>
+        <v>3.9048</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9103</v>
+        <v>1.9236</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9805</v>
+        <v>1.9812</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7065</v>
+        <v>1.6947</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2988</v>
+        <v>1.2928</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1842</v>
+        <v>2.2101</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6115</v>
+        <v>0.6308</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5727</v>
+        <v>1.5793</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1228</v>
+        <v>0.028</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8861</v>
+        <v>-0.7692</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7633</v>
+        <v>0.7972</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2403</v>
+        <v>4.1455</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1429</v>
+        <v>0.1994</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0974</v>
+        <v>3.9461</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8717</v>
+        <v>1.8525</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.8838</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7401</v>
+        <v>2.7363</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7872</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8061</v>
+        <v>1.8365</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0587</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8873</v>
+        <v>1.8951</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4972</v>
+        <v>-0.5688</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9739</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4766</v>
+        <v>0.2886</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6748</v>
+        <v>1.9616</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2301</v>
+        <v>1.4589</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4447</v>
+        <v>0.5027</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8373</v>
+        <v>1.8526</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0769</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7726</v>
+        <v>1.7758</v>
       </c>
       <c r="J17" t="n">
-        <v>1.399</v>
+        <v>1.3942</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4383</v>
+        <v>0.4584</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5916</v>
+        <v>-0.3251</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3297</v>
+        <v>-0.0931</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2619</v>
+        <v>-0.232</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1819</v>
+        <v>1.8278</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4716</v>
+        <v>-0.3898</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6535</v>
+        <v>2.2177</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1533</v>
+        <v>2.1486</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1085</v>
+        <v>2.1109</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4772</v>
+        <v>2.4494</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6992</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7539</v>
+        <v>1.7501</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3239</v>
+        <v>-0.3007</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4932</v>
+        <v>-0.8444</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0434</v>
+        <v>-0.9271</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4497</v>
+        <v>0.0827</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0751</v>
+        <v>1.0877</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0549</v>
+        <v>-0.3051</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0202</v>
+        <v>1.3928</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6229</v>
+        <v>-0.6078</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0488</v>
+        <v>0.0624</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6717</v>
+        <v>-0.6703</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0156</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6384</v>
+        <v>-0.6166</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1167</v>
+        <v>-0.1255</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0393</v>
+        <v>-0.3139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1561</v>
+        <v>0.1884</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8273</v>
+        <v>-0.3273</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8286</v>
+        <v>1.0363</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6559</v>
+        <v>-1.3636</v>
       </c>
       <c r="G20" t="n">
-        <v>3.858</v>
+        <v>3.8645</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5785</v>
+        <v>2.5818</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2795</v>
+        <v>1.2827</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0224</v>
+        <v>3.0033</v>
       </c>
       <c r="K20" t="n">
-        <v>3.0997</v>
+        <v>3.0854</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8356</v>
+        <v>0.8613</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3568</v>
+        <v>1.3648</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0217</v>
+        <v>-0.5364</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1869</v>
+        <v>0.0631</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.6636</v>
+        <v>-3.6554</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6178</v>
+        <v>-2.3778</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2305</v>
+        <v>-2.0759</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3873</v>
+        <v>-0.3018</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7094</v>
+        <v>-1.7045</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7041</v>
+        <v>-1.7032</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0053</v>
+        <v>-0.0013</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.82</v>
+        <v>-0.8298</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9415</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8894</v>
+        <v>-0.8747</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4753</v>
+        <v>0.7153</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1735</v>
+        <v>0.3505</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3018</v>
+        <v>0.3648</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3378</v>
+        <v>-2.9219</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4352</v>
+        <v>-3.3164</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9025</v>
+        <v>0.3946</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1087</v>
+        <v>1.1455</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1891</v>
+        <v>0.7552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9196</v>
+        <v>0.3903</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4326</v>
+        <v>0.5291</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0248</v>
+        <v>1.2443</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4078</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3239</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8357</v>
+        <v>-0.4891</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5118</v>
+        <v>1.1055</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0855</v>
+        <v>-1.295</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6261</v>
+        <v>-0.9758</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4594</v>
+        <v>-0.3191</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6765</v>
+        <v>-2.947</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2847</v>
+        <v>-2.3574</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3918</v>
+        <v>-0.5896</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1409</v>
+        <v>1.1074</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7517</v>
+        <v>0.1868</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3892</v>
+        <v>0.9206</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5453</v>
+        <v>1.4082</v>
       </c>
       <c r="K23" t="n">
-        <v>1.257</v>
+        <v>1.0062</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7117</v>
+        <v>0.4019</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5956</v>
+        <v>-0.3007</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5053</v>
+        <v>-0.8194</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1009</v>
+        <v>0.5187</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0442</v>
+        <v>-0.6886</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9739</v>
+        <v>-0.5089</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0704</v>
+        <v>-0.1797</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.098400000000005</v>
+        <v>11.47</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9182999999999995</v>
+        <v>-1.2298</v>
       </c>
       <c r="F24" t="n">
-        <v>10.0168</v>
+        <v>12.7001</v>
       </c>
       <c r="G24" t="n">
-        <v>17.7655</v>
+        <v>17.7849</v>
       </c>
       <c r="H24" t="n">
-        <v>4.797599999999999</v>
+        <v>4.81</v>
       </c>
       <c r="I24" t="n">
-        <v>12.9679</v>
+        <v>12.9749</v>
       </c>
       <c r="J24" t="n">
-        <v>14.1274</v>
+        <v>13.9102</v>
       </c>
       <c r="K24" t="n">
-        <v>10.0096</v>
+        <v>9.845700000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>4.118</v>
+        <v>4.0642</v>
       </c>
       <c r="M24" t="n">
-        <v>3.638100000000001</v>
+        <v>3.875</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.212</v>
+        <v>-5.0358</v>
       </c>
       <c r="O24" t="n">
-        <v>8.850099999999999</v>
+        <v>8.910600000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>3.402600000000001</v>
+        <v>3.4146</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.6102</v>
+        <v>-13.6582</v>
       </c>
       <c r="R24" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.6387</v>
+        <v>-4.2967</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.549799999999999</v>
+        <v>-5.554199999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.089</v>
+        <v>1.2576</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.431000000000001</v>
+        <v>-5.432600000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>4.1139</v>
+        <v>4.0722</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.544999999999998</v>
+        <v>-9.5046</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104672_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104672_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.0863</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.0722</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104672_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.5046</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
